--- a/ИБ/Lab03_NumberTheory/Эратосфен.xlsx
+++ b/ИБ/Lab03_NumberTheory/Эратосфен.xlsx
@@ -9,19 +9,51 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24972" windowHeight="10152"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9384"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Всего простых</t>
+    <t>делим на 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> делим на 3</t>
+  </si>
+  <si>
+    <t>делим на 5</t>
+  </si>
+  <si>
+    <t>делим на 7</t>
+  </si>
+  <si>
+    <t>делим на 11</t>
+  </si>
+  <si>
+    <t>делим на 13</t>
+  </si>
+  <si>
+    <t>делим на 17</t>
+  </si>
+  <si>
+    <t>делим на 19</t>
+  </si>
+  <si>
+    <t>делим на 23</t>
+  </si>
+  <si>
+    <t>простые числа :</t>
   </si>
 </sst>
 </file>
@@ -37,12 +69,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,8 +107,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -122,9 +177,9 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -157,9 +212,9 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -339,338 +394,1170 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:AI25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="13.77734375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="5">
         <v>587</v>
       </c>
-      <c r="B1" t="str">
-        <f t="array" aca="1" ref="B1" ca="1">IF(SUM(IF(MOD(A1,ROW(INDIRECT("2:"&amp;INT(SQRT(A1)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="B1" s="5">
         <v>588</v>
       </c>
-      <c r="B2" t="str">
-        <f t="array" aca="1" ref="B2" ca="1">IF(SUM(IF(MOD(A2,ROW(INDIRECT("2:"&amp;INT(SQRT(A2)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
+      <c r="C1" s="5">
         <v>589</v>
       </c>
-      <c r="B3" t="str">
-        <f t="array" aca="1" ref="B3" ca="1">IF(SUM(IF(MOD(A3,ROW(INDIRECT("2:"&amp;INT(SQRT(A3)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
+      <c r="D1" s="5">
         <v>590</v>
       </c>
-      <c r="B4" t="str">
-        <f t="array" aca="1" ref="B4" ca="1">IF(SUM(IF(MOD(A4,ROW(INDIRECT("2:"&amp;INT(SQRT(A4)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
+      <c r="E1" s="5">
         <v>591</v>
       </c>
-      <c r="B5" t="str">
-        <f t="array" aca="1" ref="B5" ca="1">IF(SUM(IF(MOD(A5,ROW(INDIRECT("2:"&amp;INT(SQRT(A5)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
+      <c r="F1" s="5">
         <v>592</v>
       </c>
-      <c r="B6" t="str">
-        <f t="array" aca="1" ref="B6" ca="1">IF(SUM(IF(MOD(A6,ROW(INDIRECT("2:"&amp;INT(SQRT(A6)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
+      <c r="G1" s="5">
         <v>593</v>
       </c>
-      <c r="B7" t="str">
-        <f t="array" aca="1" ref="B7" ca="1">IF(SUM(IF(MOD(A7,ROW(INDIRECT("2:"&amp;INT(SQRT(A7)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="H1" s="5">
         <v>594</v>
       </c>
-      <c r="B8" t="str">
-        <f t="array" aca="1" ref="B8" ca="1">IF(SUM(IF(MOD(A8,ROW(INDIRECT("2:"&amp;INT(SQRT(A8)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
+      <c r="I1" s="5">
         <v>595</v>
       </c>
-      <c r="B9" t="str">
-        <f t="array" aca="1" ref="B9" ca="1">IF(SUM(IF(MOD(A9,ROW(INDIRECT("2:"&amp;INT(SQRT(A9)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
+      <c r="J1" s="5">
         <v>596</v>
       </c>
-      <c r="B10" t="str">
-        <f t="array" aca="1" ref="B10" ca="1">IF(SUM(IF(MOD(A10,ROW(INDIRECT("2:"&amp;INT(SQRT(A10)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
+      <c r="K1" s="5">
         <v>597</v>
       </c>
-      <c r="B11" t="str">
-        <f t="array" aca="1" ref="B11" ca="1">IF(SUM(IF(MOD(A11,ROW(INDIRECT("2:"&amp;INT(SQRT(A11)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
+      <c r="L1" s="5">
         <v>598</v>
       </c>
-      <c r="B12" t="str">
-        <f t="array" aca="1" ref="B12" ca="1">IF(SUM(IF(MOD(A12,ROW(INDIRECT("2:"&amp;INT(SQRT(A12)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="M1" s="5">
         <v>599</v>
       </c>
-      <c r="B13" t="str">
-        <f t="array" aca="1" ref="B13" ca="1">IF(SUM(IF(MOD(A13,ROW(INDIRECT("2:"&amp;INT(SQRT(A13)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
+      <c r="N1" s="5">
         <v>600</v>
       </c>
-      <c r="B14" t="str">
-        <f t="array" aca="1" ref="B14" ca="1">IF(SUM(IF(MOD(A14,ROW(INDIRECT("2:"&amp;INT(SQRT(A14)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
+      <c r="O1" s="5">
         <v>601</v>
       </c>
-      <c r="B15" t="str">
-        <f t="array" aca="1" ref="B15" ca="1">IF(SUM(IF(MOD(A15,ROW(INDIRECT("2:"&amp;INT(SQRT(A15)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
+      <c r="P1" s="5">
         <v>602</v>
       </c>
-      <c r="B16" t="str">
-        <f t="array" aca="1" ref="B16" ca="1">IF(SUM(IF(MOD(A16,ROW(INDIRECT("2:"&amp;INT(SQRT(A16)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
+      <c r="Q1" s="5">
         <v>603</v>
       </c>
-      <c r="B17" t="str">
-        <f t="array" aca="1" ref="B17" ca="1">IF(SUM(IF(MOD(A17,ROW(INDIRECT("2:"&amp;INT(SQRT(A17)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
+      <c r="R1" s="5">
         <v>604</v>
       </c>
-      <c r="B18" t="str">
-        <f t="array" aca="1" ref="B18" ca="1">IF(SUM(IF(MOD(A18,ROW(INDIRECT("2:"&amp;INT(SQRT(A18)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
+      <c r="S1" s="5">
         <v>605</v>
       </c>
-      <c r="B19" t="str">
-        <f t="array" aca="1" ref="B19" ca="1">IF(SUM(IF(MOD(A19,ROW(INDIRECT("2:"&amp;INT(SQRT(A19)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="T1" s="5">
         <v>606</v>
       </c>
-      <c r="B20" t="str">
-        <f t="array" aca="1" ref="B20" ca="1">IF(SUM(IF(MOD(A20,ROW(INDIRECT("2:"&amp;INT(SQRT(A20)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="U1" s="5">
         <v>607</v>
       </c>
-      <c r="B21" t="str">
-        <f t="array" aca="1" ref="B21" ca="1">IF(SUM(IF(MOD(A21,ROW(INDIRECT("2:"&amp;INT(SQRT(A21)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
+      <c r="V1" s="5">
         <v>608</v>
       </c>
-      <c r="B22" t="str">
-        <f t="array" aca="1" ref="B22" ca="1">IF(SUM(IF(MOD(A22,ROW(INDIRECT("2:"&amp;INT(SQRT(A22)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
+      <c r="W1" s="5">
         <v>609</v>
       </c>
-      <c r="B23" t="str">
-        <f t="array" aca="1" ref="B23" ca="1">IF(SUM(IF(MOD(A23,ROW(INDIRECT("2:"&amp;INT(SQRT(A23)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
+      <c r="X1" s="5">
         <v>610</v>
       </c>
-      <c r="B24" t="str">
-        <f t="array" aca="1" ref="B24" ca="1">IF(SUM(IF(MOD(A24,ROW(INDIRECT("2:"&amp;INT(SQRT(A24)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
+      <c r="Y1" s="5">
         <v>611</v>
       </c>
-      <c r="B25" t="str">
-        <f t="array" aca="1" ref="B25" ca="1">IF(SUM(IF(MOD(A25,ROW(INDIRECT("2:"&amp;INT(SQRT(A25)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26">
+      <c r="Z1" s="5">
         <v>612</v>
       </c>
-      <c r="B26" t="str">
-        <f t="array" aca="1" ref="B26" ca="1">IF(SUM(IF(MOD(A26,ROW(INDIRECT("2:"&amp;INT(SQRT(A26)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27">
+      <c r="AA1" s="5">
         <v>613</v>
       </c>
-      <c r="B27" t="str">
-        <f t="array" aca="1" ref="B27" ca="1">IF(SUM(IF(MOD(A27,ROW(INDIRECT("2:"&amp;INT(SQRT(A27)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28">
+      <c r="AB1" s="5">
         <v>614</v>
       </c>
-      <c r="B28" t="str">
-        <f t="array" aca="1" ref="B28" ca="1">IF(SUM(IF(MOD(A28,ROW(INDIRECT("2:"&amp;INT(SQRT(A28)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29">
+      <c r="AC1" s="5">
         <v>615</v>
       </c>
-      <c r="B29" t="str">
-        <f t="array" aca="1" ref="B29" ca="1">IF(SUM(IF(MOD(A29,ROW(INDIRECT("2:"&amp;INT(SQRT(A29)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30">
+      <c r="AD1" s="5">
         <v>616</v>
       </c>
-      <c r="B30" t="str">
-        <f t="array" aca="1" ref="B30" ca="1">IF(SUM(IF(MOD(A30,ROW(INDIRECT("2:"&amp;INT(SQRT(A30)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31">
+      <c r="AE1" s="5">
         <v>617</v>
       </c>
-      <c r="B31" t="str">
-        <f t="array" aca="1" ref="B31" ca="1">IF(SUM(IF(MOD(A31,ROW(INDIRECT("2:"&amp;INT(SQRT(A31)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32">
+      <c r="AF1" s="5">
         <v>618</v>
       </c>
-      <c r="B32" t="str">
-        <f t="array" aca="1" ref="B32" ca="1">IF(SUM(IF(MOD(A32,ROW(INDIRECT("2:"&amp;INT(SQRT(A32)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33">
+      <c r="AG1" s="5">
         <v>619</v>
       </c>
-      <c r="B33" t="str">
-        <f t="array" aca="1" ref="B33" ca="1">IF(SUM(IF(MOD(A33,ROW(INDIRECT("2:"&amp;INT(SQRT(A33)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Простое</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34">
+      <c r="AH1" s="5">
         <v>620</v>
       </c>
-      <c r="B34" t="str">
-        <f t="array" aca="1" ref="B34" ca="1">IF(SUM(IF(MOD(A34,ROW(INDIRECT("2:"&amp;INT(SQRT(A34)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35">
+      <c r="AI1" s="5">
         <v>621</v>
       </c>
-      <c r="B35" t="str">
-        <f t="array" aca="1" ref="B35" ca="1">IF(SUM(IF(MOD(A35,ROW(INDIRECT("2:"&amp;INT(SQRT(A35)))))=0,1,0))&gt;0,"Составное","Простое")</f>
-        <v>Составное</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B36">
-        <f ca="1">COUNTIF(B1:B35, "*Простое*")</f>
+      <c r="B2" s="1"/>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>587</v>
+      </c>
+      <c r="B3" s="2">
+        <v>588</v>
+      </c>
+      <c r="C3" s="4">
+        <v>589</v>
+      </c>
+      <c r="D3" s="2">
+        <v>590</v>
+      </c>
+      <c r="E3" s="4">
+        <v>591</v>
+      </c>
+      <c r="F3" s="2">
+        <v>592</v>
+      </c>
+      <c r="G3" s="4">
+        <v>593</v>
+      </c>
+      <c r="H3" s="2">
+        <v>594</v>
+      </c>
+      <c r="I3" s="4">
+        <v>595</v>
+      </c>
+      <c r="J3" s="2">
+        <v>596</v>
+      </c>
+      <c r="K3" s="4">
+        <v>597</v>
+      </c>
+      <c r="L3" s="2">
+        <v>598</v>
+      </c>
+      <c r="M3" s="4">
+        <v>599</v>
+      </c>
+      <c r="N3" s="2">
+        <v>600</v>
+      </c>
+      <c r="O3" s="4">
+        <v>601</v>
+      </c>
+      <c r="P3" s="2">
+        <v>602</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>603</v>
+      </c>
+      <c r="R3" s="2">
+        <v>604</v>
+      </c>
+      <c r="S3" s="4">
+        <v>605</v>
+      </c>
+      <c r="T3" s="2">
+        <v>606</v>
+      </c>
+      <c r="U3" s="4">
+        <v>607</v>
+      </c>
+      <c r="V3" s="2">
+        <v>608</v>
+      </c>
+      <c r="W3" s="4">
+        <v>609</v>
+      </c>
+      <c r="X3" s="2">
+        <v>610</v>
+      </c>
+      <c r="Y3" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z3" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA3" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>614</v>
+      </c>
+      <c r="AC3" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD3" s="2">
+        <v>616</v>
+      </c>
+      <c r="AE3" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF3" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH3" s="2">
+        <v>620</v>
+      </c>
+      <c r="AI3" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1"/>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>587</v>
+      </c>
+      <c r="B5" s="2">
+        <v>588</v>
+      </c>
+      <c r="C5" s="4">
+        <v>589</v>
+      </c>
+      <c r="D5" s="4">
+        <v>590</v>
+      </c>
+      <c r="E5" s="2">
+        <v>591</v>
+      </c>
+      <c r="F5" s="4">
+        <v>592</v>
+      </c>
+      <c r="G5" s="4">
+        <v>593</v>
+      </c>
+      <c r="H5" s="2">
+        <v>594</v>
+      </c>
+      <c r="I5" s="4">
+        <v>595</v>
+      </c>
+      <c r="J5" s="4">
+        <v>596</v>
+      </c>
+      <c r="K5" s="2">
+        <v>597</v>
+      </c>
+      <c r="L5" s="4">
+        <v>598</v>
+      </c>
+      <c r="M5" s="4">
+        <v>599</v>
+      </c>
+      <c r="N5" s="2">
+        <v>600</v>
+      </c>
+      <c r="O5" s="4">
+        <v>601</v>
+      </c>
+      <c r="P5" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>603</v>
+      </c>
+      <c r="R5" s="4">
+        <v>604</v>
+      </c>
+      <c r="S5" s="4">
+        <v>605</v>
+      </c>
+      <c r="T5" s="2">
+        <v>606</v>
+      </c>
+      <c r="U5" s="4">
+        <v>607</v>
+      </c>
+      <c r="V5" s="4">
+        <v>608</v>
+      </c>
+      <c r="W5" s="2">
+        <v>609</v>
+      </c>
+      <c r="X5" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA5" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB5" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>615</v>
+      </c>
+      <c r="AD5" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE5" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF5" s="2">
+        <v>618</v>
+      </c>
+      <c r="AG5" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH5" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI5" s="2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>587</v>
+      </c>
+      <c r="B7" s="4">
+        <v>588</v>
+      </c>
+      <c r="C7" s="4">
+        <v>589</v>
+      </c>
+      <c r="D7" s="2">
+        <v>590</v>
+      </c>
+      <c r="E7" s="4">
+        <v>591</v>
+      </c>
+      <c r="F7" s="4">
+        <v>592</v>
+      </c>
+      <c r="G7" s="4">
+        <v>593</v>
+      </c>
+      <c r="H7" s="4">
+        <v>594</v>
+      </c>
+      <c r="I7" s="2">
+        <v>595</v>
+      </c>
+      <c r="J7" s="4">
+        <v>596</v>
+      </c>
+      <c r="K7" s="4">
+        <v>597</v>
+      </c>
+      <c r="L7" s="4">
+        <v>598</v>
+      </c>
+      <c r="M7" s="4">
+        <v>599</v>
+      </c>
+      <c r="N7" s="2">
+        <v>600</v>
+      </c>
+      <c r="O7" s="4">
+        <v>601</v>
+      </c>
+      <c r="P7" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>603</v>
+      </c>
+      <c r="R7" s="4">
+        <v>604</v>
+      </c>
+      <c r="S7" s="2">
+        <v>605</v>
+      </c>
+      <c r="T7" s="4">
+        <v>606</v>
+      </c>
+      <c r="U7" s="4">
+        <v>607</v>
+      </c>
+      <c r="V7" s="4">
+        <v>608</v>
+      </c>
+      <c r="W7" s="4">
+        <v>609</v>
+      </c>
+      <c r="X7" s="2">
+        <v>610</v>
+      </c>
+      <c r="Y7" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z7" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA7" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB7" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>615</v>
+      </c>
+      <c r="AD7" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE7" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF7" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH7" s="2">
+        <v>620</v>
+      </c>
+      <c r="AI7" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1"/>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>587</v>
+      </c>
+      <c r="B9" s="2">
+        <v>588</v>
+      </c>
+      <c r="C9" s="4">
+        <v>589</v>
+      </c>
+      <c r="D9" s="4">
+        <v>590</v>
+      </c>
+      <c r="E9" s="4">
+        <v>591</v>
+      </c>
+      <c r="F9" s="4">
+        <v>592</v>
+      </c>
+      <c r="G9" s="4">
+        <v>593</v>
+      </c>
+      <c r="H9" s="4">
+        <v>594</v>
+      </c>
+      <c r="I9" s="2">
+        <v>595</v>
+      </c>
+      <c r="J9" s="4">
+        <v>596</v>
+      </c>
+      <c r="K9" s="4">
+        <v>597</v>
+      </c>
+      <c r="L9" s="4">
+        <v>598</v>
+      </c>
+      <c r="M9" s="4">
+        <v>599</v>
+      </c>
+      <c r="N9" s="4">
+        <v>600</v>
+      </c>
+      <c r="O9" s="4">
+        <v>601</v>
+      </c>
+      <c r="P9" s="2">
+        <v>602</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>603</v>
+      </c>
+      <c r="R9" s="4">
+        <v>604</v>
+      </c>
+      <c r="S9" s="4">
+        <v>605</v>
+      </c>
+      <c r="T9" s="4">
+        <v>606</v>
+      </c>
+      <c r="U9" s="4">
+        <v>607</v>
+      </c>
+      <c r="V9" s="4">
+        <v>608</v>
+      </c>
+      <c r="W9" s="2">
+        <v>609</v>
+      </c>
+      <c r="X9" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y9" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z9" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA9" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB9" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC9" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>616</v>
+      </c>
+      <c r="AE9" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG9" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH9" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI9" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1"/>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>587</v>
+      </c>
+      <c r="B11" s="4">
+        <v>588</v>
+      </c>
+      <c r="C11" s="4">
+        <v>589</v>
+      </c>
+      <c r="D11" s="4">
+        <v>590</v>
+      </c>
+      <c r="E11" s="4">
+        <v>591</v>
+      </c>
+      <c r="F11" s="4">
+        <v>592</v>
+      </c>
+      <c r="G11" s="4">
+        <v>593</v>
+      </c>
+      <c r="H11" s="2">
+        <v>594</v>
+      </c>
+      <c r="I11" s="4">
+        <v>595</v>
+      </c>
+      <c r="J11" s="4">
+        <v>596</v>
+      </c>
+      <c r="K11" s="4">
+        <v>597</v>
+      </c>
+      <c r="L11" s="4">
+        <v>598</v>
+      </c>
+      <c r="M11" s="4">
+        <v>599</v>
+      </c>
+      <c r="N11" s="4">
+        <v>600</v>
+      </c>
+      <c r="O11" s="4">
+        <v>601</v>
+      </c>
+      <c r="P11" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>603</v>
+      </c>
+      <c r="R11" s="4">
+        <v>604</v>
+      </c>
+      <c r="S11" s="2">
+        <v>605</v>
+      </c>
+      <c r="T11" s="4">
+        <v>606</v>
+      </c>
+      <c r="U11" s="4">
+        <v>607</v>
+      </c>
+      <c r="V11" s="4">
+        <v>608</v>
+      </c>
+      <c r="W11" s="4">
+        <v>609</v>
+      </c>
+      <c r="X11" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y11" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z11" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA11" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB11" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC11" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD11" s="2">
+        <v>616</v>
+      </c>
+      <c r="AE11" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF11" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG11" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH11" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI11" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="1"/>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>587</v>
+      </c>
+      <c r="B13" s="4">
+        <v>588</v>
+      </c>
+      <c r="C13" s="4">
+        <v>589</v>
+      </c>
+      <c r="D13" s="4">
+        <v>590</v>
+      </c>
+      <c r="E13" s="4">
+        <v>591</v>
+      </c>
+      <c r="F13" s="4">
+        <v>592</v>
+      </c>
+      <c r="G13" s="4">
+        <v>593</v>
+      </c>
+      <c r="H13" s="4">
+        <v>594</v>
+      </c>
+      <c r="I13" s="4">
+        <v>595</v>
+      </c>
+      <c r="J13" s="4">
+        <v>596</v>
+      </c>
+      <c r="K13" s="4">
+        <v>597</v>
+      </c>
+      <c r="L13" s="2">
+        <v>598</v>
+      </c>
+      <c r="M13" s="4">
+        <v>599</v>
+      </c>
+      <c r="N13" s="4">
+        <v>600</v>
+      </c>
+      <c r="O13" s="4">
+        <v>601</v>
+      </c>
+      <c r="P13" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>603</v>
+      </c>
+      <c r="R13" s="4">
+        <v>604</v>
+      </c>
+      <c r="S13" s="4">
+        <v>605</v>
+      </c>
+      <c r="T13" s="4">
+        <v>606</v>
+      </c>
+      <c r="U13" s="4">
+        <v>607</v>
+      </c>
+      <c r="V13" s="4">
+        <v>608</v>
+      </c>
+      <c r="W13" s="4">
+        <v>609</v>
+      </c>
+      <c r="X13" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y13" s="2">
+        <v>611</v>
+      </c>
+      <c r="Z13" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA13" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB13" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC13" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD13" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE13" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF13" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG13" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH13" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI13" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>587</v>
+      </c>
+      <c r="B15" s="4">
+        <v>588</v>
+      </c>
+      <c r="C15" s="4">
+        <v>589</v>
+      </c>
+      <c r="D15" s="4">
+        <v>590</v>
+      </c>
+      <c r="E15" s="4">
+        <v>591</v>
+      </c>
+      <c r="F15" s="4">
+        <v>592</v>
+      </c>
+      <c r="G15" s="4">
+        <v>593</v>
+      </c>
+      <c r="H15" s="4">
+        <v>594</v>
+      </c>
+      <c r="I15" s="2">
+        <v>595</v>
+      </c>
+      <c r="J15" s="4">
+        <v>596</v>
+      </c>
+      <c r="K15" s="4">
+        <v>597</v>
+      </c>
+      <c r="L15" s="4">
+        <v>598</v>
+      </c>
+      <c r="M15" s="4">
+        <v>599</v>
+      </c>
+      <c r="N15" s="4">
+        <v>600</v>
+      </c>
+      <c r="O15" s="4">
+        <v>601</v>
+      </c>
+      <c r="P15" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>603</v>
+      </c>
+      <c r="R15" s="4">
+        <v>604</v>
+      </c>
+      <c r="S15" s="4">
+        <v>605</v>
+      </c>
+      <c r="T15" s="4">
+        <v>606</v>
+      </c>
+      <c r="U15" s="4">
+        <v>607</v>
+      </c>
+      <c r="V15" s="4">
+        <v>608</v>
+      </c>
+      <c r="W15" s="4">
+        <v>609</v>
+      </c>
+      <c r="X15" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y15" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z15" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA15" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB15" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC15" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD15" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE15" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF15" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG15" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH15" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI15" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>587</v>
+      </c>
+      <c r="B17" s="4">
+        <v>588</v>
+      </c>
+      <c r="C17" s="2">
+        <v>589</v>
+      </c>
+      <c r="D17" s="4">
+        <v>590</v>
+      </c>
+      <c r="E17" s="4">
+        <v>591</v>
+      </c>
+      <c r="F17" s="4">
+        <v>592</v>
+      </c>
+      <c r="G17" s="4">
+        <v>593</v>
+      </c>
+      <c r="H17" s="4">
+        <v>594</v>
+      </c>
+      <c r="I17" s="4">
+        <v>595</v>
+      </c>
+      <c r="J17" s="4">
+        <v>596</v>
+      </c>
+      <c r="K17" s="4">
+        <v>597</v>
+      </c>
+      <c r="L17" s="4">
+        <v>598</v>
+      </c>
+      <c r="M17" s="4">
+        <v>599</v>
+      </c>
+      <c r="N17" s="4">
+        <v>600</v>
+      </c>
+      <c r="O17" s="4">
+        <v>601</v>
+      </c>
+      <c r="P17" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>603</v>
+      </c>
+      <c r="R17" s="4">
+        <v>604</v>
+      </c>
+      <c r="S17" s="4">
+        <v>605</v>
+      </c>
+      <c r="T17" s="4">
+        <v>606</v>
+      </c>
+      <c r="U17" s="4">
+        <v>607</v>
+      </c>
+      <c r="V17" s="2">
+        <v>608</v>
+      </c>
+      <c r="W17" s="4">
+        <v>609</v>
+      </c>
+      <c r="X17" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y17" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z17" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA17" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB17" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC17" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD17" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE17" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF17" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG17" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH17" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI17" s="4">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>587</v>
+      </c>
+      <c r="B19" s="4">
+        <v>588</v>
+      </c>
+      <c r="C19" s="4">
+        <v>589</v>
+      </c>
+      <c r="D19" s="4">
+        <v>590</v>
+      </c>
+      <c r="E19" s="4">
+        <v>591</v>
+      </c>
+      <c r="F19" s="4">
+        <v>592</v>
+      </c>
+      <c r="G19" s="4">
+        <v>593</v>
+      </c>
+      <c r="H19" s="4">
+        <v>594</v>
+      </c>
+      <c r="I19" s="4">
+        <v>595</v>
+      </c>
+      <c r="J19" s="4">
+        <v>596</v>
+      </c>
+      <c r="K19" s="4">
+        <v>597</v>
+      </c>
+      <c r="L19" s="2">
+        <v>598</v>
+      </c>
+      <c r="M19" s="4">
+        <v>599</v>
+      </c>
+      <c r="N19" s="4">
+        <v>600</v>
+      </c>
+      <c r="O19" s="4">
+        <v>601</v>
+      </c>
+      <c r="P19" s="4">
+        <v>602</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>603</v>
+      </c>
+      <c r="R19" s="4">
+        <v>604</v>
+      </c>
+      <c r="S19" s="4">
+        <v>605</v>
+      </c>
+      <c r="T19" s="4">
+        <v>606</v>
+      </c>
+      <c r="U19" s="4">
+        <v>607</v>
+      </c>
+      <c r="V19" s="4">
+        <v>608</v>
+      </c>
+      <c r="W19" s="4">
+        <v>609</v>
+      </c>
+      <c r="X19" s="4">
+        <v>610</v>
+      </c>
+      <c r="Y19" s="4">
+        <v>611</v>
+      </c>
+      <c r="Z19" s="4">
+        <v>612</v>
+      </c>
+      <c r="AA19" s="4">
+        <v>613</v>
+      </c>
+      <c r="AB19" s="4">
+        <v>614</v>
+      </c>
+      <c r="AC19" s="4">
+        <v>615</v>
+      </c>
+      <c r="AD19" s="4">
+        <v>616</v>
+      </c>
+      <c r="AE19" s="4">
+        <v>617</v>
+      </c>
+      <c r="AF19" s="4">
+        <v>618</v>
+      </c>
+      <c r="AG19" s="4">
+        <v>619</v>
+      </c>
+      <c r="AH19" s="4">
+        <v>620</v>
+      </c>
+      <c r="AI19" s="2">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>587</v>
+      </c>
+      <c r="B22" s="1">
+        <v>593</v>
+      </c>
+      <c r="C22" s="1">
+        <v>599</v>
+      </c>
+      <c r="D22" s="1">
+        <v>601</v>
+      </c>
+      <c r="E22" s="1">
+        <v>607</v>
+      </c>
+      <c r="F22" s="1">
+        <v>613</v>
+      </c>
+      <c r="G22" s="1">
+        <v>617</v>
+      </c>
+      <c r="H22" s="1">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="H25" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>